--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_PANATHINAIKOS AKTOR ATHENS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_PANATHINAIKOS AKTOR ATHENS.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>366.5599999999999</v>
+        <v>439.0799999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>365.8</v>
+        <v>438.44</v>
       </c>
       <c r="D2" t="n">
-        <v>118.917441224713</v>
+        <v>113.8126083386552</v>
       </c>
       <c r="E2" t="n">
-        <v>117.8239475123018</v>
+        <v>116.7776662713256</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5451895043731778</v>
+        <v>0.526829268292683</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1257100288667474</v>
+        <v>0.1305839245341857</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3288888888888889</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1778425655976676</v>
+        <v>0.1634146341463415</v>
       </c>
       <c r="J2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M2" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="N2" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="O2" t="n">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5218658892128279</v>
+        <v>0.5097560975609756</v>
       </c>
       <c r="Q2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R2" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2186588921282799</v>
+        <v>0.2048780487804878</v>
       </c>
       <c r="T2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04373177842565597</v>
+        <v>0.04146341463414634</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04664723032069971</v>
+        <v>0.05365853658536585</v>
       </c>
       <c r="Z2" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AA2" t="n">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3469387755102041</v>
+        <v>0.3536585365853658</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7430167597765364</v>
+        <v>0.7177033492822966</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.52</v>
+        <v>0.4880952380952381</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1875</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.361344537815126</v>
+        <v>0.3517241379310345</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.486033519553073</v>
+        <v>1.435406698564593</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.022222222222222</v>
+        <v>1.005988023952096</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7868852459016393</v>
+        <v>0.7323943661971831</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.19047619047619</v>
+        <v>1.189189189189189</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.62962962962963</v>
+        <v>1.507462686567164</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.351851851851852</v>
+        <v>6.119402985074627</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.981481481481482</v>
+        <v>7.626865671641791</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.31199999999998</v>
+        <v>73.17999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>73.16</v>
+        <v>73.07333333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>118.917441224713</v>
+        <v>113.8126083386552</v>
       </c>
       <c r="E3" t="n">
-        <v>117.8239475123018</v>
+        <v>116.7776662713256</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5451895043731778</v>
+        <v>0.526829268292683</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1257100288667474</v>
+        <v>0.1305839245341857</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3288888888888889</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1778425655976676</v>
+        <v>0.1634146341463415</v>
       </c>
       <c r="J3" t="n">
-        <v>9.6</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
-        <v>35.8</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5218658892128279</v>
+        <v>0.5097560975609757</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.8</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="R3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2186588921282799</v>
+        <v>0.2048780487804878</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04373177842565598</v>
+        <v>0.04146341463414634</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="X3" t="n">
-        <v>3.2</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04664723032069971</v>
+        <v>0.05365853658536585</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.8</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3469387755102041</v>
+        <v>0.3536585365853659</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7430167597765364</v>
+        <v>0.7177033492822966</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.52</v>
+        <v>0.4880952380952381</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1875</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.361344537815126</v>
+        <v>0.3517241379310345</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.486033519553073</v>
+        <v>1.435406698564593</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9411764705882352</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.022222222222222</v>
+        <v>1.005988023952096</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7868852459016393</v>
+        <v>0.732394366197183</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.19047619047619</v>
+        <v>1.189189189189189</v>
       </c>
       <c r="AM3" t="n">
         <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.62962962962963</v>
+        <v>1.507462686567164</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.351851851851851</v>
+        <v>6.119402985074626</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.98148148148148</v>
+        <v>7.626865671641791</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>365.04</v>
+        <v>437.8</v>
       </c>
       <c r="C4" t="n">
-        <v>365.8</v>
+        <v>438.44</v>
       </c>
       <c r="D4" t="n">
-        <v>117.8239475123018</v>
+        <v>116.7776662713256</v>
       </c>
       <c r="E4" t="n">
-        <v>118.917441224713</v>
+        <v>113.8126083386552</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5547112462006079</v>
+        <v>0.539440203562341</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1418472700213934</v>
+        <v>0.1373839009287926</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3672316384180791</v>
+        <v>0.3623853211009174</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2006079027355623</v>
+        <v>0.2239185750636132</v>
       </c>
       <c r="J4" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="L4" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="M4" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N4" t="n">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="O4" t="n">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5197568389057751</v>
+        <v>0.5521628498727735</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="S4" t="n">
-        <v>0.182370820668693</v>
+        <v>0.1730279898218829</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0303951367781155</v>
+        <v>0.02798982188295165</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07598784194528875</v>
+        <v>0.08396946564885496</v>
       </c>
       <c r="Z4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="AA4" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.39209726443769</v>
+        <v>0.3867684478371501</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8362573099415205</v>
+        <v>0.8248847926267281</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3970588235294117</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.32</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3178294573643411</v>
+        <v>0.3092105263157895</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.672514619883041</v>
+        <v>1.649769585253456</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9405405405405406</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.7910447761194029</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9076923076923077</v>
+        <v>0.9240506329113924</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.82051282051282</v>
+        <v>1.775510204081633</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.672131147540984</v>
+        <v>1.661971830985915</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.39344262295082</v>
+        <v>5.535211267605634</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.065573770491803</v>
+        <v>7.197183098591549</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.00800000000001</v>
+        <v>72.96666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>73.16</v>
+        <v>73.07333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>117.8239475123018</v>
+        <v>116.7776662713256</v>
       </c>
       <c r="E5" t="n">
-        <v>118.917441224713</v>
+        <v>113.8126083386552</v>
       </c>
       <c r="F5" t="n">
-        <v>0.554711246200608</v>
+        <v>0.5394402035623409</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1418472700213934</v>
+        <v>0.1373839009287926</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3672316384180791</v>
+        <v>0.3623853211009174</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2006079027355623</v>
+        <v>0.2239185750636132</v>
       </c>
       <c r="J5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>11.8</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="M5" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>28.6</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>34.2</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5197568389057752</v>
+        <v>0.5521628498727735</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
-        <v>12</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="S5" t="n">
-        <v>0.182370820668693</v>
+        <v>0.173027989821883</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0303951367781155</v>
+        <v>0.02798982188295165</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07598784194528875</v>
+        <v>0.08396946564885496</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="AA5" t="n">
-        <v>25.8</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.39209726443769</v>
+        <v>0.3867684478371501</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8362573099415205</v>
+        <v>0.8248847926267281</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3970588235294117</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636365</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.32</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.317829457364341</v>
+        <v>0.3092105263157895</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.672514619883041</v>
+        <v>1.649769585253456</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9545454545454545</v>
+        <v>0.9405405405405406</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8148148148148149</v>
+        <v>0.791044776119403</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9076923076923078</v>
+        <v>0.9240506329113924</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.82051282051282</v>
+        <v>1.775510204081633</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.672131147540984</v>
+        <v>1.661971830985915</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.39344262295082</v>
+        <v>5.535211267605633</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.065573770491802</v>
+        <v>7.197183098591549</v>
       </c>
     </row>
     <row r="7">
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>63</v>
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
         <v>9</v>
@@ -1456,7 +1456,7 @@
         <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1477,13 +1477,13 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U8" t="n">
         <v>10</v>
@@ -1510,10 +1510,10 @@
         <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.286</v>
+        <v>0.267</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1537,54 +1537,54 @@
         <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.444</v>
+        <v>0.4</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>171:50</t>
+          <t>187:35</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>61.96</v>
+        <v>63.96</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.491</v>
+        <v>0.474</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.534</v>
+        <v>0.517</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.017</v>
+        <v>0.985</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.164</v>
+        <v>0.158</v>
       </c>
       <c r="AU8" t="n">
         <v>5.333</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.333</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>23.667</v>
+        <v>24.333</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.172</v>
+        <v>0.163</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.115</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="9">
@@ -1759,43 +1759,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
         <v>22</v>
       </c>
-      <c r="F10" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>18</v>
       </c>
-      <c r="H10" t="n">
-        <v>16</v>
-      </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
         <v>7</v>
       </c>
       <c r="M10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" t="n">
         <v>4</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1807,19 +1807,19 @@
         <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T10" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="U10" t="n">
         <v>10</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>4</v>
@@ -1828,13 +1828,13 @@
         <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1864,57 +1864,57 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.412</v>
+        <v>0.429</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>307:33</t>
+          <t>348:17</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>53.36</v>
+        <v>63.12</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.588</v>
+        <v>0.573</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.651</v>
+        <v>0.628</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.181</v>
+        <v>1.157</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.094</v>
+        <v>0.079</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.083</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11">
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="12">
@@ -2089,22 +2089,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H12" t="n">
         <v>15</v>
@@ -2119,7 +2119,7 @@
         <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
         <v>7</v>
@@ -2131,25 +2131,25 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
         <v>7</v>
@@ -2158,93 +2158,93 @@
         <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="AB12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.6</v>
+        <v>0.526</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.267</v>
+        <v>0.297</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>316:26</t>
+          <t>380:06</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>69.48</v>
+        <v>85.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.414</v>
+        <v>0.438</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.481</v>
+        <v>0.491</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.907</v>
+        <v>0.912</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.058</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.259</v>
+        <v>0.208</v>
       </c>
       <c r="AU12" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="AV12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>16.5</v>
+        <v>13.333</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.056</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="13">
@@ -2254,67 +2254,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>6</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -2323,13 +2323,13 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="AB13" t="n">
         <v>5</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2362,54 +2362,54 @@
         <v>5</v>
       </c>
       <c r="AL13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>138:39</t>
+          <t>171:38</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>27.88</v>
+        <v>32.76</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.635</v>
+        <v>0.569</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.651</v>
+        <v>0.601</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.255</v>
+        <v>1.129</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.036</v>
+        <v>0.061</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.077</v>
+        <v>0.138</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV13" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.053</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="14">
@@ -2419,22 +2419,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
@@ -2443,19 +2443,19 @@
         <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2467,13 +2467,13 @@
         <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -2482,28 +2482,28 @@
         <v>3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.538</v>
+        <v>0.533</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2524,57 +2524,57 @@
         <v>0.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.143</v>
+        <v>0.2</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>237:15</t>
+          <t>298:11</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>34.64</v>
+        <v>40.64</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.4</v>
+        <v>0.435</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.452</v>
+        <v>0.476</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.722</v>
+        <v>0.787</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.202</v>
+        <v>0.172</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.2</v>
+        <v>0.161</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>4.429</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.571</v>
+        <v>4.429</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.571</v>
+        <v>8.856999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.135</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="15">
@@ -2584,22 +2584,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
@@ -2608,13 +2608,13 @@
         <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>5</v>
@@ -2626,49 +2626,49 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q15" t="n">
+        <v>18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>18</v>
+      </c>
+      <c r="S15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" t="n">
-        <v>15</v>
-      </c>
-      <c r="S15" t="n">
-        <v>8</v>
-      </c>
       <c r="T15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V15" t="n">
         <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.737</v>
+        <v>0.68</v>
       </c>
       <c r="AB15" t="n">
         <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.727</v>
+        <v>0.667</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2683,63 +2683,63 @@
         <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.167</v>
+        <v>0.125</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL15" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.458</v>
+        <v>0.429</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>308:07</t>
+          <t>356:53</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>73.08</v>
+        <v>92.08</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.649</v>
+        <v>0.593</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.657</v>
+        <v>0.602</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.081</v>
+        <v>0.956</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.178</v>
+        <v>0.206</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>0.737</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.385</v>
+        <v>3.684</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.385</v>
+        <v>4.421</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.113</v>
+        <v>0.123</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.098</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="16">
@@ -2749,16 +2749,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2779,13 +2779,13 @@
         <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2797,19 +2797,19 @@
         <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T16" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="U16" t="n">
         <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2818,22 +2818,22 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.714</v>
+        <v>0.706</v>
       </c>
       <c r="AB16" t="n">
         <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2864,47 +2864,47 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>217:45</t>
+          <t>241:31</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>41.96</v>
+        <v>49.96</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.61</v>
+        <v>0.588</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.929</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.238</v>
+        <v>0.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.25</v>
+        <v>0.194</v>
       </c>
       <c r="AU16" t="n">
         <v>0.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.092</v>
+        <v>0.099</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.079</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.047</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="17">
@@ -2914,28 +2914,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
@@ -2944,13 +2944,13 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2983,93 +2983,93 @@
         <v>1</v>
       </c>
       <c r="Y17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
         <v>2</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1</v>
-      </c>
       <c r="AL17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>31:34</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>14.88</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.583</v>
+        <v>0.54</v>
       </c>
       <c r="AR17" t="n">
-        <v>1</v>
+        <v>1.008</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.143</v>
+        <v>0.067</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AU17" t="n">
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.469</v>
+        <v>0.225</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.163</v>
+        <v>0.036</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="18">
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
         <v>17</v>
@@ -3088,7 +3088,7 @@
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
         <v>6</v>
@@ -3121,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>6</v>
@@ -3133,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3151,10 +3151,10 @@
         <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.8</v>
+        <v>0.727</v>
       </c>
       <c r="AB18" t="n">
         <v>1</v>
@@ -3194,44 +3194,44 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>81:53</t>
+          <t>109:26</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>13.88</v>
+        <v>15.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.667</v>
+        <v>0.615</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.66</v>
+        <v>0.612</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.225</v>
+        <v>1.071</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.126</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.081</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
@@ -3259,46 +3259,46 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -3352,54 +3352,54 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>31:28</t>
+          <t>49:49</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.7</v>
+        <v>0.583</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.7</v>
+        <v>0.583</v>
       </c>
       <c r="AR19" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.106</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.037</v>
+        <v>0.113</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="20">
@@ -3409,22 +3409,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="n">
         <v>6</v>
       </c>
-      <c r="E20" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5</v>
-      </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -3433,13 +3433,13 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
@@ -3457,19 +3457,19 @@
         <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
         <v>8</v>
@@ -3478,13 +3478,13 @@
         <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="AB20" t="n">
         <v>1</v>
@@ -3505,66 +3505,66 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK20" t="n">
         <v>5</v>
       </c>
       <c r="AL20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>166:14</t>
+          <t>198:48</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>23.44</v>
+        <v>27.44</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.711</v>
+        <v>0.696</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.694</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.152</v>
+        <v>1.166</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.171</v>
+        <v>0.146</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.061</v>
+        <v>0.055</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.098</v>
+        <v>0.107</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="21">
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>27:24</t>
+          <t>37:48</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3720,13 +3720,13 @@
         <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.052</v>
+        <v>0.038</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.041</v>
+        <v>0.029</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.042</v>
+        <v>0.03</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -3766,10 +3766,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3781,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -4069,159 +4069,159 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>499</v>
+      </c>
+      <c r="D24" t="n">
+        <v>132</v>
+      </c>
+      <c r="E24" t="n">
+        <v>243</v>
+      </c>
+      <c r="F24" t="n">
+        <v>56</v>
+      </c>
+      <c r="G24" t="n">
+        <v>167</v>
+      </c>
+      <c r="H24" t="n">
+        <v>67</v>
+      </c>
+      <c r="I24" t="n">
+        <v>82</v>
+      </c>
+      <c r="J24" t="n">
+        <v>101</v>
+      </c>
+      <c r="K24" t="n">
+        <v>139</v>
+      </c>
+      <c r="L24" t="n">
+        <v>74</v>
+      </c>
+      <c r="M24" t="n">
+        <v>45</v>
+      </c>
+      <c r="N24" t="n">
+        <v>34</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>61</v>
+      </c>
+      <c r="R24" t="n">
+        <v>112</v>
+      </c>
+      <c r="S24" t="n">
+        <v>103</v>
+      </c>
+      <c r="T24" t="n">
+        <v>579</v>
+      </c>
+      <c r="U24" t="n">
+        <v>52</v>
+      </c>
+      <c r="V24" t="n">
+        <v>88</v>
+      </c>
+      <c r="W24" t="n">
+        <v>34</v>
+      </c>
+      <c r="X24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>150</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>209</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AH24" t="n">
         <v>5</v>
       </c>
-      <c r="C24" t="n">
-        <v>435</v>
-      </c>
-      <c r="D24" t="n">
-        <v>118</v>
-      </c>
-      <c r="E24" t="n">
-        <v>208</v>
-      </c>
-      <c r="F24" t="n">
-        <v>46</v>
-      </c>
-      <c r="G24" t="n">
-        <v>135</v>
-      </c>
-      <c r="H24" t="n">
-        <v>61</v>
-      </c>
-      <c r="I24" t="n">
-        <v>74</v>
-      </c>
-      <c r="J24" t="n">
-        <v>88</v>
-      </c>
-      <c r="K24" t="n">
-        <v>112</v>
-      </c>
-      <c r="L24" t="n">
-        <v>63</v>
-      </c>
-      <c r="M24" t="n">
-        <v>41</v>
-      </c>
-      <c r="N24" t="n">
-        <v>24</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>50</v>
-      </c>
-      <c r="R24" t="n">
-        <v>92</v>
-      </c>
-      <c r="S24" t="n">
-        <v>84</v>
-      </c>
-      <c r="T24" t="n">
-        <v>509</v>
-      </c>
-      <c r="U24" t="n">
-        <v>48</v>
-      </c>
-      <c r="V24" t="n">
-        <v>75</v>
-      </c>
-      <c r="W24" t="n">
-        <v>30</v>
-      </c>
-      <c r="X24" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>133</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>179</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>39</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3</v>
-      </c>
       <c r="AI24" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.188</v>
+        <v>0.227</v>
       </c>
       <c r="AK24" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AL24" t="n">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.361</v>
+        <v>0.352</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1025:00</t>
+          <t>1225:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>429.56</v>
+        <v>513.08</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.545</v>
+        <v>0.527</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.579</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.013</v>
+        <v>0.973</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.126</v>
+        <v>0.131</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.178</v>
+        <v>0.163</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.63</v>
+        <v>1.507</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.352</v>
+        <v>6.119</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.981</v>
+        <v>7.627</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="BA24" t="n">
         <v>0</v>
@@ -4234,159 +4234,159 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>431</v>
+        <v>512</v>
       </c>
       <c r="D25" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E25" t="n">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="F25" t="n">
+        <v>58</v>
+      </c>
+      <c r="G25" t="n">
+        <v>185</v>
+      </c>
+      <c r="H25" t="n">
+        <v>88</v>
+      </c>
+      <c r="I25" t="n">
+        <v>120</v>
+      </c>
+      <c r="J25" t="n">
+        <v>118</v>
+      </c>
+      <c r="K25" t="n">
+        <v>151</v>
+      </c>
+      <c r="L25" t="n">
+        <v>79</v>
+      </c>
+      <c r="M25" t="n">
+        <v>42</v>
+      </c>
+      <c r="N25" t="n">
+        <v>34</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>66</v>
+      </c>
+      <c r="R25" t="n">
+        <v>95</v>
+      </c>
+      <c r="S25" t="n">
+        <v>120</v>
+      </c>
+      <c r="T25" t="n">
+        <v>648</v>
+      </c>
+      <c r="U25" t="n">
+        <v>53</v>
+      </c>
+      <c r="V25" t="n">
+        <v>73</v>
+      </c>
+      <c r="W25" t="n">
+        <v>87</v>
+      </c>
+      <c r="X25" t="n">
         <v>49</v>
       </c>
-      <c r="G25" t="n">
-        <v>154</v>
-      </c>
-      <c r="H25" t="n">
-        <v>66</v>
-      </c>
-      <c r="I25" t="n">
-        <v>91</v>
-      </c>
-      <c r="J25" t="n">
-        <v>102</v>
-      </c>
-      <c r="K25" t="n">
-        <v>119</v>
-      </c>
-      <c r="L25" t="n">
-        <v>65</v>
-      </c>
-      <c r="M25" t="n">
-        <v>35</v>
-      </c>
-      <c r="N25" t="n">
-        <v>24</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>58</v>
-      </c>
-      <c r="R25" t="n">
-        <v>79</v>
-      </c>
-      <c r="S25" t="n">
-        <v>98</v>
-      </c>
-      <c r="T25" t="n">
-        <v>538</v>
-      </c>
-      <c r="U25" t="n">
-        <v>44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>59</v>
-      </c>
-      <c r="W25" t="n">
-        <v>71</v>
-      </c>
-      <c r="X25" t="n">
-        <v>39</v>
-      </c>
       <c r="Y25" t="n">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="Z25" t="n">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.836</v>
+        <v>0.825</v>
       </c>
       <c r="AB25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC25" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.433</v>
+        <v>0.397</v>
       </c>
       <c r="AE25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.6</v>
+        <v>0.636</v>
       </c>
       <c r="AH25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI25" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.32</v>
+        <v>0.333</v>
       </c>
       <c r="AK25" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="AL25" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.318</v>
+        <v>0.309</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1025:00</t>
+          <t>1225:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>430.04</v>
+        <v>516.8</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.555</v>
+        <v>0.539</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.584</v>
+        <v>0.574</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.002</v>
+        <v>0.991</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.142</v>
+        <v>0.137</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.201</v>
+        <v>0.224</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.672</v>
+        <v>1.662</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.393</v>
+        <v>5.535</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.066</v>
+        <v>7.197</v>
       </c>
       <c r="AX25" t="n">
         <v>0.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.131</v>
+        <v>0.134</v>
       </c>
       <c r="BA25" t="n">
         <v>0</v>
@@ -4458,97 +4458,97 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>12.6</v>
+        <v>10.5</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="E27" t="n">
-        <v>9.199999999999999</v>
+        <v>7.833</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="G27" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>2.667</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="W27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="X27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
         <v>0.667</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.286</v>
+        <v>0.267</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AG27" t="n">
         <v>0.4</v>
@@ -4563,57 +4563,57 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.444</v>
+        <v>0.4</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>34:22</t>
+          <t>31:15</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>12.392</v>
+        <v>10.66</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.491</v>
+        <v>0.474</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.534</v>
+        <v>0.517</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.017</v>
+        <v>0.985</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.164</v>
+        <v>0.158</v>
       </c>
       <c r="AU27" t="n">
         <v>5.333</v>
       </c>
       <c r="AV27" t="n">
-        <v>18.333</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
-        <v>23.667</v>
+        <v>24.333</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.172</v>
+        <v>0.163</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.115</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="28">
@@ -4788,88 +4788,88 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>12.6</v>
+        <v>12.167</v>
       </c>
       <c r="D29" t="n">
-        <v>2.6</v>
+        <v>2.333</v>
       </c>
       <c r="E29" t="n">
-        <v>4.4</v>
+        <v>4.333</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G29" t="n">
-        <v>3.6</v>
+        <v>3.667</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>3.833</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>4.333</v>
       </c>
       <c r="L29" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>3.333</v>
       </c>
       <c r="T29" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="V29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="X29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Z29" t="n">
         <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="AD29" t="n">
         <v>0.625</v>
@@ -4887,63 +4887,63 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.412</v>
+        <v>0.429</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>61:30</t>
+          <t>58:02</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>10.672</v>
+        <v>10.52</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.587</v>
+        <v>0.573</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.651</v>
+        <v>0.628</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.181</v>
+        <v>1.157</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.094</v>
+        <v>0.079</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AU29" t="n">
         <v>1</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.083</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="30">
@@ -5108,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.168</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="31">
@@ -5118,162 +5118,162 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="E31" t="n">
-        <v>5.2</v>
+        <v>5.333</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6</v>
+        <v>1.833</v>
       </c>
       <c r="G31" t="n">
-        <v>6.4</v>
+        <v>6.667</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>2.833</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="K31" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="L31" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="S31" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="T31" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="W31" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="X31" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.6</v>
+        <v>3.167</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.4</v>
+        <v>3.833</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="AC31" t="n">
-        <v>3</v>
+        <v>3.167</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.6</v>
+        <v>0.526</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AJ31" t="n">
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.6</v>
+        <v>1.833</v>
       </c>
       <c r="AL31" t="n">
-        <v>6</v>
+        <v>6.167</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.267</v>
+        <v>0.297</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>63:17</t>
+          <t>63:21</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>13.896</v>
+        <v>14.247</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.414</v>
+        <v>0.438</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.481</v>
+        <v>0.491</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.907</v>
+        <v>0.912</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.058</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.259</v>
+        <v>0.208</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="AV31" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>16.5</v>
+        <v>13.333</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.056</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="32">
@@ -5283,88 +5283,88 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>6.167</v>
       </c>
       <c r="D32" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
-        <v>2.6</v>
+        <v>2.333</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="G32" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="J32" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="K32" t="n">
-        <v>1.4</v>
+        <v>1.667</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="N32" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="T32" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="U32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AA32" t="n">
         <v>0.8</v>
       </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.857</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="AD32" t="n">
         <v>0.625</v>
@@ -5382,63 +5382,63 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>27:43</t>
+          <t>28:36</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>5.576</v>
+        <v>5.46</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.635</v>
+        <v>0.569</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.651</v>
+        <v>0.601</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.255</v>
+        <v>1.129</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.036</v>
+        <v>0.061</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.077</v>
+        <v>0.138</v>
       </c>
       <c r="AU32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV32" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.053</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="33">
@@ -5448,162 +5448,162 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>5.333</v>
       </c>
       <c r="D33" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E33" t="n">
-        <v>3.2</v>
+        <v>3.167</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>4.2</v>
+        <v>5.167</v>
       </c>
       <c r="K33" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M33" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>2.2</v>
+        <v>2.333</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8</v>
+        <v>1.167</v>
       </c>
       <c r="T33" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U33" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.538</v>
+        <v>0.533</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AC33" t="n">
         <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AG33" t="n">
         <v>1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AJ33" t="n">
         <v>0.5</v>
       </c>
       <c r="AK33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AM33" t="n">
         <v>0.2</v>
       </c>
-      <c r="AL33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.143</v>
-      </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>47:27</t>
+          <t>49:41</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.928</v>
+        <v>6.773</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.4</v>
+        <v>0.435</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.452</v>
+        <v>0.476</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.722</v>
+        <v>0.787</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.202</v>
+        <v>0.172</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.2</v>
+        <v>0.161</v>
       </c>
       <c r="AU33" t="n">
-        <v>3</v>
+        <v>4.429</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.571</v>
+        <v>4.429</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.571</v>
+        <v>8.856999999999999</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.135</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="34">
@@ -5613,162 +5613,162 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>15.8</v>
+        <v>14.667</v>
       </c>
       <c r="D34" t="n">
-        <v>3.8</v>
+        <v>3.667</v>
       </c>
       <c r="E34" t="n">
-        <v>5.4</v>
+        <v>5.667</v>
       </c>
       <c r="F34" t="n">
-        <v>2.4</v>
+        <v>2.167</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="J34" t="n">
-        <v>2.6</v>
+        <v>2.333</v>
       </c>
       <c r="K34" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>3.167</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
         <v>3</v>
       </c>
       <c r="S34" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U34" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.8</v>
+        <v>2.833</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.8</v>
+        <v>4.167</v>
       </c>
       <c r="AA34" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>59:28</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>15.347</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AU34" t="n">
         <v>0.737</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>61:37</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>14.616</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.657</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.081</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1</v>
-      </c>
       <c r="AV34" t="n">
-        <v>4.385</v>
+        <v>3.684</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.385</v>
+        <v>4.421</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.113</v>
+        <v>0.123</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.098</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="35">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>7.8</v>
+        <v>7.833</v>
       </c>
       <c r="D35" t="n">
-        <v>3.2</v>
+        <v>3.333</v>
       </c>
       <c r="E35" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5796,49 +5796,49 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="K35" t="n">
-        <v>3.4</v>
+        <v>2.833</v>
       </c>
       <c r="L35" t="n">
-        <v>2.8</v>
+        <v>2.833</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="R35" t="n">
-        <v>2.4</v>
+        <v>2.667</v>
       </c>
       <c r="S35" t="n">
-        <v>3.8</v>
+        <v>3.667</v>
       </c>
       <c r="T35" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="U35" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5850,19 +5850,19 @@
         <v>4</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.6</v>
+        <v>5.667</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.714</v>
+        <v>0.706</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -5893,47 +5893,47 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>43:33</t>
+          <t>40:15</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>8.391999999999999</v>
+        <v>8.327</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.61</v>
+        <v>0.588</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.929</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.238</v>
+        <v>0.2</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.25</v>
+        <v>0.194</v>
       </c>
       <c r="AU35" t="n">
         <v>0.7</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.092</v>
+        <v>0.099</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.09</v>
+        <v>0.079</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.047</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="36">
@@ -5943,83 +5943,83 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>2.333</v>
+        <v>3.75</v>
       </c>
       <c r="D36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T36" t="n">
+        <v>16</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA36" t="n">
         <v>0.667</v>
       </c>
-      <c r="E36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="T36" t="n">
-        <v>6</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1</v>
-      </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
@@ -6033,72 +6033,72 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.333</v>
+        <v>1.75</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>02:22</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>2.333</v>
+        <v>3.72</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.583</v>
+        <v>0.54</v>
       </c>
       <c r="AR36" t="n">
-        <v>1</v>
+        <v>1.008</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.143</v>
+        <v>0.067</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AU36" t="n">
         <v>2</v>
       </c>
       <c r="AV36" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.469</v>
+        <v>0.225</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.163</v>
+        <v>0.036</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="37">
@@ -6108,16 +6108,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>3.4</v>
+        <v>2.833</v>
       </c>
       <c r="D37" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="E37" t="n">
-        <v>2.4</v>
+        <v>2.167</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -6126,70 +6126,70 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1.4</v>
+        <v>1.667</v>
       </c>
       <c r="L37" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="N37" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="T37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2.6</v>
+        <v>2.167</v>
       </c>
       <c r="W37" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="X37" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.8</v>
+        <v>0.727</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD37" t="n">
         <v>0.333</v>
@@ -6223,44 +6223,44 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>2.776</v>
+        <v>2.647</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.667</v>
+        <v>0.615</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.66</v>
+        <v>0.612</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.225</v>
+        <v>1.071</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.126</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="AU37" t="n">
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.081</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6273,22 +6273,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>2.333</v>
+        <v>1.75</v>
       </c>
       <c r="D38" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F38" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="G38" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K38" t="n">
-        <v>0.333</v>
+        <v>1.25</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -6315,19 +6315,19 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="R38" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -6342,19 +6342,19 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AA38" t="n">
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AD38" t="n">
         <v>0.5</v>
@@ -6369,66 +6369,66 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AS38" t="n">
         <v>0.333</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
         <v>0.333</v>
       </c>
-      <c r="AJ38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
+      <c r="AV38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW38" t="n">
         <v>2.333</v>
       </c>
-      <c r="AP38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AX38" t="n">
-        <v>0.106</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.037</v>
+        <v>0.113</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="39">
@@ -6438,162 +6438,162 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>5.4</v>
+        <v>5.333</v>
       </c>
       <c r="D39" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="E39" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="K39" t="n">
-        <v>2.8</v>
+        <v>3.167</v>
       </c>
       <c r="L39" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="T39" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="U39" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="X39" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Y39" t="n">
         <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AA39" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.833</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1</v>
       </c>
       <c r="AL39" t="n">
         <v>2</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>33:14</t>
+          <t>33:08</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>4.688</v>
+        <v>4.573</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.711</v>
+        <v>0.696</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.694</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.152</v>
+        <v>1.166</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.171</v>
+        <v>0.146</v>
       </c>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV39" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.061</v>
+        <v>0.055</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.098</v>
+        <v>0.107</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="40">
@@ -6603,22 +6603,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -6630,10 +6630,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -6651,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -6672,10 +6672,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AA40" t="n">
         <v>0.5</v>
@@ -6711,18 +6711,18 @@
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>05:28</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP40" t="n">
         <v>0.333</v>
@@ -6749,13 +6749,13 @@
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.052</v>
+        <v>0.038</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.041</v>
+        <v>0.029</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.042</v>
+        <v>0.03</v>
       </c>
       <c r="BA40" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -6795,10 +6795,10 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1.6</v>
+        <v>1.667</v>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -6810,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6933,7 +6933,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="AP42" t="n">
         <v>0</v>
@@ -7098,159 +7098,159 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>87</v>
+        <v>83.167</v>
       </c>
       <c r="D43" t="n">
-        <v>23.6</v>
+        <v>22</v>
       </c>
       <c r="E43" t="n">
-        <v>41.6</v>
+        <v>40.5</v>
       </c>
       <c r="F43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.333</v>
       </c>
       <c r="G43" t="n">
-        <v>27</v>
+        <v>27.833</v>
       </c>
       <c r="H43" t="n">
-        <v>12.2</v>
+        <v>11.167</v>
       </c>
       <c r="I43" t="n">
-        <v>14.8</v>
+        <v>13.667</v>
       </c>
       <c r="J43" t="n">
-        <v>17.6</v>
+        <v>16.833</v>
       </c>
       <c r="K43" t="n">
-        <v>22.4</v>
+        <v>23.167</v>
       </c>
       <c r="L43" t="n">
-        <v>12.6</v>
+        <v>12.333</v>
       </c>
       <c r="M43" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="N43" t="n">
-        <v>4.8</v>
+        <v>5.667</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>10.8</v>
+        <v>11.167</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>10.167</v>
       </c>
       <c r="R43" t="n">
-        <v>18.4</v>
+        <v>18.667</v>
       </c>
       <c r="S43" t="n">
-        <v>16.8</v>
+        <v>17.167</v>
       </c>
       <c r="T43" t="n">
-        <v>509</v>
+        <v>579</v>
       </c>
       <c r="U43" t="n">
-        <v>9.6</v>
+        <v>8.667</v>
       </c>
       <c r="V43" t="n">
-        <v>15</v>
+        <v>14.667</v>
       </c>
       <c r="W43" t="n">
-        <v>6</v>
+        <v>5.667</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>2.833</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="Z43" t="n">
-        <v>35.8</v>
+        <v>34.833</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.743</v>
+        <v>0.718</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.8</v>
+        <v>6.833</v>
       </c>
       <c r="AC43" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.52</v>
+        <v>0.488</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AF43" t="n">
-        <v>3</v>
+        <v>2.833</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.467</v>
+        <v>0.471</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.2</v>
+        <v>3.667</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.187</v>
+        <v>0.227</v>
       </c>
       <c r="AK43" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AL43" t="n">
-        <v>23.8</v>
+        <v>24.167</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.361</v>
+        <v>0.352</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>205:00</t>
+          <t>204:10</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>85.91200000000001</v>
+        <v>85.51300000000001</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.545</v>
+        <v>0.527</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.579</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.013</v>
+        <v>0.973</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.126</v>
+        <v>0.131</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.178</v>
+        <v>0.163</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.63</v>
+        <v>1.507</v>
       </c>
       <c r="AV43" t="n">
-        <v>6.352</v>
+        <v>6.119</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.981</v>
+        <v>7.627</v>
       </c>
       <c r="AX43" t="n">
         <v>0.2</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="BA43" t="n">
         <v>0</v>
@@ -7263,159 +7263,159 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>86.2</v>
+        <v>85.333</v>
       </c>
       <c r="D44" t="n">
-        <v>21.8</v>
+        <v>20.833</v>
       </c>
       <c r="E44" t="n">
-        <v>35</v>
+        <v>34.667</v>
       </c>
       <c r="F44" t="n">
-        <v>9.800000000000001</v>
+        <v>9.667</v>
       </c>
       <c r="G44" t="n">
-        <v>30.8</v>
+        <v>30.833</v>
       </c>
       <c r="H44" t="n">
-        <v>13.2</v>
+        <v>14.667</v>
       </c>
       <c r="I44" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>20.4</v>
+        <v>19.667</v>
       </c>
       <c r="K44" t="n">
-        <v>23.8</v>
+        <v>25.167</v>
       </c>
       <c r="L44" t="n">
-        <v>13</v>
+        <v>13.167</v>
       </c>
       <c r="M44" t="n">
         <v>7</v>
       </c>
       <c r="N44" t="n">
-        <v>4.8</v>
+        <v>5.667</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>12.2</v>
+        <v>11.833</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="R44" t="n">
-        <v>15.8</v>
+        <v>15.833</v>
       </c>
       <c r="S44" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="T44" t="n">
-        <v>538</v>
+        <v>648</v>
       </c>
       <c r="U44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.833</v>
       </c>
       <c r="V44" t="n">
-        <v>11.8</v>
+        <v>12.167</v>
       </c>
       <c r="W44" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="X44" t="n">
-        <v>7.8</v>
+        <v>8.167</v>
       </c>
       <c r="Y44" t="n">
-        <v>28.6</v>
+        <v>29.833</v>
       </c>
       <c r="Z44" t="n">
-        <v>34.2</v>
+        <v>36.167</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.836</v>
+        <v>0.825</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>12</v>
+        <v>11.333</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.433</v>
+        <v>0.397</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.6</v>
+        <v>0.636</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.6</v>
+        <v>1.833</v>
       </c>
       <c r="AI44" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.32</v>
+        <v>0.333</v>
       </c>
       <c r="AK44" t="n">
-        <v>8.199999999999999</v>
+        <v>7.833</v>
       </c>
       <c r="AL44" t="n">
-        <v>25.8</v>
+        <v>25.333</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.318</v>
+        <v>0.309</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>205:00</t>
+          <t>204:10</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>86.008</v>
+        <v>86.133</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.555</v>
+        <v>0.539</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.584</v>
+        <v>0.574</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.002</v>
+        <v>0.991</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.142</v>
+        <v>0.137</v>
       </c>
       <c r="AT44" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1.662</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>5.535</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>7.197</v>
+      </c>
+      <c r="AX44" t="n">
         <v>0.201</v>
       </c>
-      <c r="AU44" t="n">
-        <v>1.672</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>5.393</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>7.066</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0.2</v>
-      </c>
       <c r="AY44" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.134</v>
+        <v>0.139</v>
       </c>
       <c r="BA44" t="n">
         <v>0</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_PANATHINAIKOS AKTOR ATHENS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_PANATHINAIKOS AKTOR ATHENS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA44"/>
+  <dimension ref="A1:BA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.1634146341463415</v>
       </c>
       <c r="J2" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>61</v>
@@ -752,13 +752,13 @@
         <v>1.005988023952096</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7323943661971831</v>
+        <v>0.08450704225352113</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.189189189189189</v>
+        <v>0.04054054054054054</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>1.507462686567164</v>
@@ -801,13 +801,13 @@
         <v>0.1634146341463415</v>
       </c>
       <c r="J3" t="n">
-        <v>8.666666666666666</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>14.66666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>5.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>10.16666666666667</v>
@@ -882,13 +882,13 @@
         <v>1.005988023952096</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.732394366197183</v>
+        <v>0.08450704225352113</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.189189189189189</v>
+        <v>0.04054054054054054</v>
       </c>
       <c r="AM3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>1.507462686567164</v>
@@ -931,13 +931,13 @@
         <v>0.2239185750636132</v>
       </c>
       <c r="J4" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>66</v>
@@ -1012,13 +1012,13 @@
         <v>0.9405405405405406</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7910447761194029</v>
+        <v>0.07462686567164178</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9240506329113924</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.775510204081633</v>
+        <v>3</v>
       </c>
       <c r="AN4" t="n">
         <v>1.661971830985915</v>
@@ -1061,13 +1061,13 @@
         <v>0.2239185750636132</v>
       </c>
       <c r="J5" t="n">
-        <v>8.833333333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>12.16666666666667</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>14.5</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
@@ -1142,13 +1142,13 @@
         <v>0.9405405405405406</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.791044776119403</v>
+        <v>0.0746268656716418</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9240506329113924</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.775510204081633</v>
+        <v>3</v>
       </c>
       <c r="AN5" t="n">
         <v>1.661971830985915</v>
@@ -1486,16 +1486,16 @@
         <v>66</v>
       </c>
       <c r="U8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>24</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>187:35</t>
+          <t>97:34</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>24.333</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.163</v>
+        <v>0.313</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.036</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="BA8" t="n">
         <v>0.098</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.032</v>
+        <v>0.098</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -1816,16 +1816,16 @@
         <v>91</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>27</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>348:17</t>
+          <t>161:56</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>10.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.186</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.022</v>
+        <v>0.047</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="BA10" t="n">
         <v>0.03</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>30:37</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,7 +2070,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.154</v>
+        <v>0.229</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>380:06</t>
+          <t>183:45</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>13.333</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.107</v>
+        <v>0.222</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.023</v>
+        <v>0.047</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.033</v>
+        <v>0.067</v>
       </c>
       <c r="BA12" t="n">
         <v>0.049</v>
@@ -2311,16 +2311,16 @@
         <v>42</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>8</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>171:38</t>
+          <t>76:33</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>18.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.091</v>
+        <v>0.204</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.019</v>
+        <v>0.043</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.065</v>
+        <v>0.147</v>
       </c>
       <c r="BA13" t="n">
         <v>0.046</v>
@@ -2476,16 +2476,16 @@
         <v>57</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
         <v>3</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>8</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>298:11</t>
+          <t>141:47</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>8.856999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.065</v>
+        <v>0.137</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.011</v>
+        <v>0.023</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.045</v>
+        <v>0.095</v>
       </c>
       <c r="BA14" t="n">
         <v>0.176</v>
@@ -2641,16 +2641,16 @@
         <v>61</v>
       </c>
       <c r="U15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>17</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>356:53</t>
+          <t>180:33</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>4.421</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.123</v>
+        <v>0.244</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.035</v>
+        <v>0.068</v>
       </c>
       <c r="BA15" t="n">
         <v>0.092</v>
@@ -2806,10 +2806,10 @@
         <v>77</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>241:31</t>
+          <t>150:07</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>4.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.099</v>
+        <v>0.159</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.077</v>
+        <v>0.123</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.079</v>
+        <v>0.127</v>
       </c>
       <c r="BA16" t="n">
         <v>0.042</v>
@@ -2974,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>4</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>31:34</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.225</v>
+        <v>0.329</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.036</v>
+        <v>0.052</v>
       </c>
       <c r="BA17" t="n">
         <v>0.011</v>
@@ -3139,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>8</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>109:26</t>
+          <t>49:27</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>6.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.153</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.06</v>
+        <v>0.132</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.103</v>
+        <v>0.227</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>49:49</t>
+          <t>29:49</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>2.333</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.113</v>
+        <v>0.188</v>
       </c>
       <c r="BA19" t="n">
         <v>0.005</v>
@@ -3466,16 +3466,16 @@
         <v>49</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>198:48</t>
+          <t>98:42</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>6.75</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.066</v>
+        <v>0.133</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.055</v>
+        <v>0.11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.107</v>
+        <v>0.216</v>
       </c>
       <c r="BA20" t="n">
         <v>0.023</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>37:48</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3720,13 +3720,13 @@
         <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.038</v>
+        <v>0.184</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.029</v>
+        <v>0.14</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.03</v>
+        <v>0.144</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3900,71 +3900,71 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="T23" t="n">
-        <v>18</v>
+        <v>579</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -3973,90 +3973,90 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>0.718</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.471</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>1225:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>4</v>
+        <v>513.08</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>0.527</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.507</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>6.119</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>7.627</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4065,44 +4065,44 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="D24" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E24" t="n">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="F24" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G24" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="H24" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="I24" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="J24" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="K24" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="L24" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M24" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N24" t="n">
         <v>34</v>
@@ -4111,76 +4111,76 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q24" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="R24" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="S24" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="T24" t="n">
-        <v>579</v>
+        <v>648</v>
       </c>
       <c r="U24" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="Z24" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.718</v>
+        <v>0.825</v>
       </c>
       <c r="AB24" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="AC24" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.488</v>
+        <v>0.397</v>
       </c>
       <c r="AE24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF24" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.471</v>
+        <v>0.636</v>
       </c>
       <c r="AH24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AI24" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.227</v>
+        <v>0.333</v>
       </c>
       <c r="AK24" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AL24" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.352</v>
+        <v>0.309</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4188,40 +4188,40 @@
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>513.08</v>
+        <v>516.8</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.527</v>
+        <v>0.539</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.574</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.973</v>
+        <v>0.991</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.131</v>
+        <v>0.137</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.163</v>
+        <v>0.224</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.507</v>
+        <v>1.662</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.119</v>
+        <v>5.535</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.627</v>
+        <v>7.197</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.066</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.128</v>
+        <v>0.134</v>
       </c>
       <c r="BA24" t="n">
         <v>0</v>
@@ -4230,328 +4230,328 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" t="n">
-        <v>512</v>
-      </c>
-      <c r="D25" t="n">
-        <v>125</v>
-      </c>
-      <c r="E25" t="n">
-        <v>208</v>
-      </c>
-      <c r="F25" t="n">
-        <v>58</v>
-      </c>
-      <c r="G25" t="n">
-        <v>185</v>
-      </c>
-      <c r="H25" t="n">
-        <v>88</v>
-      </c>
-      <c r="I25" t="n">
-        <v>120</v>
-      </c>
-      <c r="J25" t="n">
-        <v>118</v>
-      </c>
-      <c r="K25" t="n">
-        <v>151</v>
-      </c>
-      <c r="L25" t="n">
-        <v>79</v>
-      </c>
-      <c r="M25" t="n">
-        <v>42</v>
-      </c>
-      <c r="N25" t="n">
-        <v>34</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>66</v>
-      </c>
-      <c r="R25" t="n">
-        <v>95</v>
-      </c>
-      <c r="S25" t="n">
-        <v>120</v>
-      </c>
-      <c r="T25" t="n">
-        <v>648</v>
-      </c>
-      <c r="U25" t="n">
-        <v>53</v>
-      </c>
-      <c r="V25" t="n">
-        <v>73</v>
-      </c>
-      <c r="W25" t="n">
-        <v>87</v>
-      </c>
-      <c r="X25" t="n">
-        <v>49</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>179</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>217</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>68</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>33</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>47</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>152</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>1225:00</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>516.8</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.662</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>5.535</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>7.197</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr"/>
+          <t>#0 T. SHORTS (Per Game)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.833</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>66</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>24.333</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0.098</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#0 T. SHORTS (Per Game)</t>
+          <t>#5 P. KALAITZAKIS (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>7.833</v>
+        <v>0.333</v>
       </c>
       <c r="F27" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>0.333</v>
       </c>
       <c r="T27" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0.333</v>
       </c>
-      <c r="AF27" t="n">
-        <v>0.833</v>
-      </c>
       <c r="AG27" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4563,121 +4563,121 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>31:15</t>
+          <t>01:37</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>10.66</v>
+        <v>0.333</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.474</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.517</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.985</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.333</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>24.333</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.163</v>
+        <v>0.098</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#5 P. KALAITZAKIS (Per Game)</t>
+          <t>#6 C. OSMAN (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>12.167</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="H28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>3.833</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>4.333</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
-        <v>0.333</v>
+        <v>3.333</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -4692,28 +4692,28 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -4722,157 +4722,157 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>04:57</t>
+          <t>26:59</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>0.333</v>
+        <v>10.52</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.573</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.628</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.157</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.032</v>
+        <v>0.186</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#6 C. OSMAN (Per Game)</t>
+          <t>#10 K. SLOUKAS (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
         <v>6</v>
       </c>
-      <c r="C29" t="n">
-        <v>12.167</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>3</v>
       </c>
-      <c r="I29" t="n">
-        <v>3.833</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="T29" t="n">
-        <v>91</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="V29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>4.5</v>
-      </c>
       <c r="Z29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4887,109 +4887,109 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.429</v>
+        <v>0.2</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>58:02</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>10.52</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.573</v>
+        <v>0.438</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.628</v>
+        <v>0.45</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.157</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.079</v>
+        <v>0.101</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="AU29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AW29" t="n">
-        <v>10.6</v>
+        <v>13</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.229</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.03</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#10 K. SLOUKAS (Per Game)</t>
+          <t>#11 N. HAYES-DAVIS (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>5.333</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>1.833</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>6.667</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.833</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>1.333</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -5001,13 +5001,13 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>3</v>
+        <v>1.833</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2.333</v>
       </c>
       <c r="T30" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -5022,49 +5022,49 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>3</v>
+        <v>3.167</v>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
+        <v>3.833</v>
       </c>
       <c r="AA30" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>3.167</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH30" t="n">
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>1.833</v>
       </c>
       <c r="AL30" t="n">
-        <v>5</v>
+        <v>6.167</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.2</v>
+        <v>0.297</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5072,146 +5072,146 @@
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>9.880000000000001</v>
+        <v>14.247</v>
       </c>
       <c r="AP30" t="n">
         <v>0.438</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.45</v>
+        <v>0.491</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.912</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.101</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.125</v>
+        <v>0.208</v>
       </c>
       <c r="AU30" t="n">
-        <v>5</v>
+        <v>1.333</v>
       </c>
       <c r="AV30" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AW30" t="n">
-        <v>13</v>
+        <v>13.333</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.154</v>
+        <v>0.222</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.176</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#11 N. HAYES-DAVIS (Per Game)</t>
+          <t>#17 N. ROGKAVOPOULOS (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>6.167</v>
       </c>
       <c r="D31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G31" t="n">
         <v>2.5</v>
       </c>
-      <c r="E31" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6.667</v>
-      </c>
       <c r="H31" t="n">
-        <v>2.5</v>
+        <v>0.667</v>
       </c>
       <c r="I31" t="n">
-        <v>2.833</v>
+        <v>0.667</v>
       </c>
       <c r="J31" t="n">
         <v>1.333</v>
       </c>
       <c r="K31" t="n">
-        <v>1.833</v>
+        <v>1.667</v>
       </c>
       <c r="L31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="T31" t="n">
+        <v>42</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.333</v>
       </c>
-      <c r="M31" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="Z31" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB31" t="n">
         <v>0.833</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="T31" t="n">
-        <v>66</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3.167</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.833</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.667</v>
-      </c>
       <c r="AC31" t="n">
-        <v>3.167</v>
+        <v>1.333</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.526</v>
+        <v>0.625</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5223,322 +5223,322 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.833</v>
+        <v>0.833</v>
       </c>
       <c r="AL31" t="n">
-        <v>6.167</v>
+        <v>2</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.297</v>
+        <v>0.417</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>63:21</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>14.247</v>
+        <v>5.46</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.438</v>
+        <v>0.569</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.491</v>
+        <v>0.601</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.912</v>
+        <v>1.129</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.208</v>
+        <v>0.138</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.333</v>
+        <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>13.333</v>
+        <v>18.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.107</v>
+        <v>0.204</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.023</v>
+        <v>0.043</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.033</v>
+        <v>0.147</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.049</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#17 N. ROGKAVOPOULOS (Per Game)</t>
+          <t>#22 J. GRANT (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>6.167</v>
+        <v>5.333</v>
       </c>
       <c r="D32" t="n">
         <v>1.5</v>
       </c>
       <c r="E32" t="n">
-        <v>2.333</v>
+        <v>3.167</v>
       </c>
       <c r="F32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
         <v>0.833</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.667</v>
-      </c>
       <c r="I32" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1.333</v>
+        <v>5.167</v>
       </c>
       <c r="K32" t="n">
-        <v>1.667</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>0.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0.167</v>
+        <v>1.667</v>
       </c>
       <c r="N32" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.333</v>
+        <v>1.167</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>2.333</v>
       </c>
       <c r="S32" t="n">
-        <v>0.333</v>
+        <v>1.167</v>
       </c>
       <c r="T32" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="U32" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>1.333</v>
       </c>
       <c r="Z32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AL32" t="n">
         <v>1.667</v>
       </c>
-      <c r="AA32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2</v>
-      </c>
       <c r="AM32" t="n">
-        <v>0.417</v>
+        <v>0.2</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>28:36</t>
+          <t>23:37</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>5.46</v>
+        <v>6.773</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.569</v>
+        <v>0.435</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.601</v>
+        <v>0.476</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.129</v>
+        <v>0.787</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.061</v>
+        <v>0.172</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.138</v>
+        <v>0.161</v>
       </c>
       <c r="AU32" t="n">
-        <v>4</v>
+        <v>4.429</v>
       </c>
       <c r="AV32" t="n">
-        <v>14.5</v>
+        <v>4.429</v>
       </c>
       <c r="AW32" t="n">
-        <v>18.5</v>
+        <v>8.856999999999999</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.091</v>
+        <v>0.137</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.065</v>
+        <v>0.095</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.046</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#22 J. GRANT (Per Game)</t>
+          <t>#25 K. NUNN (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>5.333</v>
+        <v>14.667</v>
       </c>
       <c r="D33" t="n">
-        <v>1.5</v>
+        <v>3.667</v>
       </c>
       <c r="E33" t="n">
-        <v>3.167</v>
+        <v>5.667</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>2.167</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
         <v>0.833</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="J33" t="n">
-        <v>5.167</v>
+        <v>2.333</v>
       </c>
       <c r="K33" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="L33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.167</v>
-      </c>
       <c r="T33" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE33" t="n">
         <v>0.333</v>
       </c>
-      <c r="V33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="AF33" t="n">
         <v>0.333</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.5</v>
       </c>
       <c r="AG33" t="n">
         <v>1</v>
@@ -5547,791 +5547,791 @@
         <v>0.167</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.333</v>
+        <v>1.333</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.333</v>
+        <v>2</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.667</v>
+        <v>4.667</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.2</v>
+        <v>0.429</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>49:41</t>
+          <t>30:05</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.773</v>
+        <v>15.347</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.435</v>
+        <v>0.593</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.476</v>
+        <v>0.602</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.787</v>
+        <v>0.956</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.172</v>
+        <v>0.206</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.161</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AU33" t="n">
-        <v>4.429</v>
+        <v>0.737</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.429</v>
+        <v>3.684</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.856999999999999</v>
+        <v>4.421</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.065</v>
+        <v>0.244</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.045</v>
+        <v>0.068</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.176</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#25 K. NUNN (Per Game)</t>
+          <t>#26 M. LESSORT (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>14.667</v>
+        <v>7.833</v>
       </c>
       <c r="D34" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.667</v>
       </c>
-      <c r="E34" t="n">
+      <c r="T34" t="n">
+        <v>77</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z34" t="n">
         <v>5.667</v>
       </c>
-      <c r="F34" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="G34" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>3.167</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>61</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="W34" t="n">
+      <c r="AA34" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD34" t="n">
         <v>0.333</v>
       </c>
-      <c r="X34" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.667</v>
-      </c>
       <c r="AE34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>4.667</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>59:28</t>
+          <t>25:01</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>15.347</v>
+        <v>8.327</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.593</v>
+        <v>0.556</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.602</v>
+        <v>0.588</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.956</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.206</v>
+        <v>0.2</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.194</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.737</v>
+        <v>0.7</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.684</v>
+        <v>3.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.421</v>
+        <v>4.3</v>
       </c>
       <c r="AX34" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AY34" t="n">
         <v>0.123</v>
       </c>
-      <c r="AY34" t="n">
-        <v>0.012</v>
-      </c>
       <c r="AZ34" t="n">
-        <v>0.035</v>
+        <v>0.127</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.092</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#26 M. LESSORT (Per Game)</t>
+          <t>#27 V. TOLIOPOULOS (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>7.833</v>
+        <v>3.75</v>
       </c>
       <c r="D35" t="n">
-        <v>3.333</v>
+        <v>0.5</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>1.25</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>1.167</v>
+        <v>0.5</v>
       </c>
       <c r="I35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T35" t="n">
+        <v>16</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.5</v>
       </c>
-      <c r="J35" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="AA35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
         <v>0.5</v>
       </c>
-      <c r="N35" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="T35" t="n">
-        <v>77</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="n">
-        <v>3</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="AL35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>05:23</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AP35" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>40:15</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>8.327</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.556</v>
-      </c>
       <c r="AQ35" t="n">
-        <v>0.588</v>
+        <v>0.54</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.008</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.2</v>
+        <v>0.067</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.194</v>
+        <v>0.154</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.099</v>
+        <v>0.329</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.077</v>
+        <v>0.101</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.079</v>
+        <v>0.052</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.042</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#27 V. TOLIOPOULOS (Per Game)</t>
+          <t>#35 K. FARIED (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>3.75</v>
+        <v>2.833</v>
       </c>
       <c r="D36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="T36" t="n">
+        <v>22</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AC36" t="n">
         <v>0.5</v>
       </c>
-      <c r="E36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T36" t="n">
-        <v>16</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>3.72</v>
+        <v>2.647</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.5</v>
+        <v>0.615</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.54</v>
+        <v>0.612</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.008</v>
+        <v>1.071</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.067</v>
+        <v>0.126</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.154</v>
+        <v>0.077</v>
       </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.225</v>
+        <v>0.153</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.036</v>
+        <v>0.227</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#35 K. FARIED (Per Game)</t>
+          <t>#40 M. GRIGONIS (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>2.833</v>
+        <v>1.75</v>
       </c>
       <c r="D37" t="n">
-        <v>1.333</v>
+        <v>0.5</v>
       </c>
       <c r="E37" t="n">
-        <v>2.167</v>
+        <v>0.75</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H37" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K37" t="n">
-        <v>1.667</v>
+        <v>1.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="N37" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.333</v>
+        <v>0.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.333</v>
+        <v>0.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S37" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="T37" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.333</v>
+        <v>0.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.833</v>
+        <v>0.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.727</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="AC37" t="n">
         <v>0.5</v>
       </c>
       <c r="AD37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AS37" t="n">
         <v>0.333</v>
       </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>2.647</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.126</v>
-      </c>
       <c r="AT37" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AV37" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.5</v>
+        <v>2.333</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.144</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.103</v>
+        <v>0.188</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#40 M. GRIGONIS (Per Game)</t>
+          <t>#41 J. HERNANGOMEZ (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>1.75</v>
+        <v>5.333</v>
       </c>
       <c r="D38" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="M38" t="n">
         <v>0.5</v>
       </c>
-      <c r="E38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.25</v>
-      </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="R38" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T38" t="n">
+        <v>49</v>
+      </c>
+      <c r="U38" t="n">
         <v>0.5</v>
       </c>
-      <c r="S38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T38" t="n">
-        <v>7</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
@@ -6342,283 +6342,283 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.25</v>
+        <v>1.167</v>
       </c>
       <c r="AA38" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AC38" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AJ38" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>2.25</v>
+        <v>4.573</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.583</v>
+        <v>0.696</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.583</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.778</v>
+        <v>1.166</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.333</v>
+        <v>0.146</v>
       </c>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AV38" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.333</v>
+        <v>6.75</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.133</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.113</v>
+        <v>0.216</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.008</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#41 J. HERNANGOMEZ (Per Game)</t>
+          <t>#44 K. MITOGLOU (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>5.333</v>
+        <v>0.333</v>
       </c>
       <c r="D39" t="n">
-        <v>1.167</v>
+        <v>0.167</v>
       </c>
       <c r="E39" t="n">
-        <v>1.333</v>
+        <v>0.333</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2.5</v>
+        <v>0.167</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>0.167</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="AO39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AR39" t="n">
         <v>0.667</v>
       </c>
-      <c r="K39" t="n">
-        <v>3.167</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="T39" t="n">
-        <v>49</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>33:08</t>
-        </is>
-      </c>
-      <c r="AO39" t="n">
-        <v>4.573</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.166</v>
-      </c>
       <c r="AS39" t="n">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.066</v>
+        <v>0.184</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.055</v>
+        <v>0.14</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.107</v>
+        <v>0.144</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#44 K. MITOGLOU (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -6630,10 +6630,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.167</v>
+        <v>1.667</v>
       </c>
       <c r="L40" t="n">
-        <v>0.167</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -6645,19 +6645,19 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -6711,27 +6711,27 @@
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
@@ -6749,13 +6749,13 @@
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
         <v>0</v>
@@ -6764,71 +6764,71 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>83.167</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>9.333</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>27.833</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>11.167</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>13.667</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>16.833</v>
       </c>
       <c r="K41" t="n">
-        <v>1.667</v>
+        <v>23.167</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>12.333</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.667</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.667</v>
+        <v>11.167</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>10.167</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>18.667</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>17.167</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -6837,90 +6837,90 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>34.833</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>0.718</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>6.833</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>0.471</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>3.667</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>24.167</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>204:10</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>85.51300000000001</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>0.527</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>1.507</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>6.119</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>7.627</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="BA41" t="n">
         <v>0</v>
@@ -6929,495 +6929,165 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>85.333</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>20.833</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>34.667</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>9.667</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>30.833</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>14.667</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>19.667</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>25.167</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>13.167</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.667</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>11.833</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>15.833</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T42" t="n">
-        <v>18</v>
+        <v>648</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>29.833</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>36.167</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>0.825</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>11.333</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>7.833</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>25.333</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>204:10</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>0.667</v>
+        <v>86.133</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>0.539</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>0.574</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>0.991</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.662</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>5.535</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>7.197</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>0.201</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>6</v>
-      </c>
-      <c r="C43" t="n">
-        <v>83.167</v>
-      </c>
-      <c r="D43" t="n">
-        <v>22</v>
-      </c>
-      <c r="E43" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F43" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="G43" t="n">
-        <v>27.833</v>
-      </c>
-      <c r="H43" t="n">
-        <v>11.167</v>
-      </c>
-      <c r="I43" t="n">
-        <v>13.667</v>
-      </c>
-      <c r="J43" t="n">
-        <v>16.833</v>
-      </c>
-      <c r="K43" t="n">
-        <v>23.167</v>
-      </c>
-      <c r="L43" t="n">
-        <v>12.333</v>
-      </c>
-      <c r="M43" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>11.167</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>10.167</v>
-      </c>
-      <c r="R43" t="n">
-        <v>18.667</v>
-      </c>
-      <c r="S43" t="n">
-        <v>17.167</v>
-      </c>
-      <c r="T43" t="n">
-        <v>579</v>
-      </c>
-      <c r="U43" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="V43" t="n">
-        <v>14.667</v>
-      </c>
-      <c r="W43" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>34.833</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>6.833</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>24.167</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>204:10</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>85.51300000000001</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1.507</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>6.119</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>7.627</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>6</v>
-      </c>
-      <c r="C44" t="n">
-        <v>85.333</v>
-      </c>
-      <c r="D44" t="n">
-        <v>20.833</v>
-      </c>
-      <c r="E44" t="n">
-        <v>34.667</v>
-      </c>
-      <c r="F44" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="G44" t="n">
-        <v>30.833</v>
-      </c>
-      <c r="H44" t="n">
-        <v>14.667</v>
-      </c>
-      <c r="I44" t="n">
-        <v>20</v>
-      </c>
-      <c r="J44" t="n">
-        <v>19.667</v>
-      </c>
-      <c r="K44" t="n">
-        <v>25.167</v>
-      </c>
-      <c r="L44" t="n">
-        <v>13.167</v>
-      </c>
-      <c r="M44" t="n">
-        <v>7</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>11.833</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>11</v>
-      </c>
-      <c r="R44" t="n">
-        <v>15.833</v>
-      </c>
-      <c r="S44" t="n">
-        <v>20</v>
-      </c>
-      <c r="T44" t="n">
-        <v>648</v>
-      </c>
-      <c r="U44" t="n">
-        <v>8.833</v>
-      </c>
-      <c r="V44" t="n">
-        <v>12.167</v>
-      </c>
-      <c r="W44" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="X44" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>29.833</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>36.167</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>11.333</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>7.833</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>25.333</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>204:10</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>86.133</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1.662</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>5.535</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>7.197</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="BA44" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_PANATHINAIKOS AKTOR ATHENS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_PANATHINAIKOS AKTOR ATHENS.xlsx
@@ -671,13 +671,13 @@
         <v>0.1634146341463415</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M2" t="n">
         <v>61</v>
@@ -752,13 +752,13 @@
         <v>1.005988023952096</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.7464788732394366</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04054054054054054</v>
+        <v>1.243243243243243</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
         <v>1.507462686567164</v>
@@ -801,13 +801,13 @@
         <v>0.1634146341463415</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="M3" t="n">
         <v>10.16666666666667</v>
@@ -882,13 +882,13 @@
         <v>1.005988023952096</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.7464788732394366</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.04054054054054054</v>
+        <v>1.243243243243243</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
         <v>1.507462686567164</v>
@@ -931,13 +931,13 @@
         <v>0.2239185750636132</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="M4" t="n">
         <v>66</v>
@@ -1012,13 +1012,13 @@
         <v>0.9405405405405406</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.07462686567164178</v>
+        <v>0.8059701492537313</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.9240506329113924</v>
       </c>
       <c r="AM4" t="n">
-        <v>3</v>
+        <v>1.678571428571429</v>
       </c>
       <c r="AN4" t="n">
         <v>1.661971830985915</v>
@@ -1061,13 +1061,13 @@
         <v>0.2239185750636132</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8333333333333334</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>15.66666666666667</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
@@ -1142,13 +1142,13 @@
         <v>0.9405405405405406</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0746268656716418</v>
+        <v>0.8059701492537313</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.9240506329113924</v>
       </c>
       <c r="AM5" t="n">
-        <v>3</v>
+        <v>1.678571428571428</v>
       </c>
       <c r="AN5" t="n">
         <v>1.661971830985915</v>
@@ -1486,16 +1486,16 @@
         <v>66</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
         <v>24</v>
@@ -1816,16 +1816,16 @@
         <v>91</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
         <v>27</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
@@ -2311,16 +2311,16 @@
         <v>42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>8</v>
@@ -2476,16 +2476,16 @@
         <v>57</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>8</v>
@@ -2641,16 +2641,16 @@
         <v>61</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>17</v>
@@ -2806,10 +2806,10 @@
         <v>77</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2974,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>4</v>
@@ -3139,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>8</v>
@@ -3466,16 +3466,16 @@
         <v>49</v>
       </c>
       <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>8</v>
+      </c>
+      <c r="X20" t="n">
         <v>3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
@@ -3961,16 +3961,16 @@
         <v>579</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y23" t="n">
         <v>150</v>
@@ -4126,16 +4126,16 @@
         <v>648</v>
       </c>
       <c r="U24" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Y24" t="n">
         <v>179</v>
@@ -4350,16 +4350,16 @@
         <v>66</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y26" t="n">
         <v>4</v>
@@ -4680,16 +4680,16 @@
         <v>91</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y28" t="n">
         <v>4.5</v>
@@ -5013,13 +5013,13 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Y30" t="n">
         <v>3.167</v>
@@ -5175,16 +5175,16 @@
         <v>42</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y31" t="n">
         <v>1.333</v>
@@ -5340,16 +5340,16 @@
         <v>57</v>
       </c>
       <c r="U32" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="V32" t="n">
         <v>0.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y32" t="n">
         <v>1.333</v>
@@ -5505,16 +5505,16 @@
         <v>61</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y33" t="n">
         <v>2.833</v>
@@ -5670,10 +5670,10 @@
         <v>77</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -5838,13 +5838,13 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y35" t="n">
         <v>1</v>
@@ -6003,13 +6003,13 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y36" t="n">
         <v>1.333</v>
@@ -6330,16 +6330,16 @@
         <v>49</v>
       </c>
       <c r="U38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="X38" t="n">
         <v>0.5</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>1</v>
@@ -6825,16 +6825,16 @@
         <v>579</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>8.833</v>
       </c>
       <c r="V41" t="n">
-        <v>0.5</v>
+        <v>15.333</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>5.667</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="Y41" t="n">
         <v>25</v>
@@ -6990,16 +6990,16 @@
         <v>648</v>
       </c>
       <c r="U42" t="n">
-        <v>0.833</v>
+        <v>9</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>12.167</v>
       </c>
       <c r="W42" t="n">
-        <v>0.5</v>
+        <v>15.667</v>
       </c>
       <c r="X42" t="n">
-        <v>0.167</v>
+        <v>9.333</v>
       </c>
       <c r="Y42" t="n">
         <v>29.833</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_PANATHINAIKOS AKTOR ATHENS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_PANATHINAIKOS AKTOR ATHENS.xlsx
@@ -683,13 +683,13 @@
         <v>61</v>
       </c>
       <c r="N2" t="n">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="O2" t="n">
-        <v>209</v>
+        <v>142</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5097560975609756</v>
+        <v>0.3463414634146341</v>
       </c>
       <c r="Q2" t="n">
         <v>41</v>
@@ -710,25 +710,25 @@
         <v>0.04146341463414634</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05365853658536585</v>
+        <v>0.06097560975609756</v>
       </c>
       <c r="Z2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AA2" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3536585365853658</v>
+        <v>0.3463414634146341</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7177033492822966</v>
+        <v>0.5845070422535211</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4880952380952381</v>
@@ -737,13 +737,13 @@
         <v>0.4705882352941176</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.28</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3517241379310345</v>
+        <v>0.3450704225352113</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.435406698564593</v>
+        <v>1.169014084507042</v>
       </c>
       <c r="AI2" t="n">
         <v>0.9411764705882353</v>
@@ -813,13 +813,13 @@
         <v>10.16666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>34.83333333333334</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5097560975609757</v>
+        <v>0.3463414634146342</v>
       </c>
       <c r="Q3" t="n">
         <v>6.833333333333333</v>
@@ -840,25 +840,25 @@
         <v>0.04146341463414634</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>3.666666666666667</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05365853658536585</v>
+        <v>0.06097560975609757</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.16666666666667</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3536585365853659</v>
+        <v>0.3463414634146342</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7177033492822966</v>
+        <v>0.5845070422535211</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4880952380952381</v>
@@ -867,13 +867,13 @@
         <v>0.4705882352941176</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.28</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3517241379310345</v>
+        <v>0.3450704225352113</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.435406698564593</v>
+        <v>1.169014084507042</v>
       </c>
       <c r="AI3" t="n">
         <v>0.9411764705882352</v>
@@ -943,13 +943,13 @@
         <v>66</v>
       </c>
       <c r="N4" t="n">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="O4" t="n">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5521628498727735</v>
+        <v>0.3282442748091603</v>
       </c>
       <c r="Q4" t="n">
         <v>27</v>
@@ -973,22 +973,22 @@
         <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08396946564885496</v>
+        <v>0.08905852417302799</v>
       </c>
       <c r="Z4" t="n">
         <v>47</v>
       </c>
       <c r="AA4" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3867684478371501</v>
+        <v>0.3816793893129771</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8248847926267281</v>
+        <v>0.7054263565891473</v>
       </c>
       <c r="AD4" t="n">
         <v>0.3970588235294117</v>
@@ -997,13 +997,13 @@
         <v>0.6363636363636364</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3092105263157895</v>
+        <v>0.3133333333333334</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.649769585253456</v>
+        <v>1.410852713178295</v>
       </c>
       <c r="AI4" t="n">
         <v>1.272727272727273</v>
@@ -1073,13 +1073,13 @@
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>29.83333333333333</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>36.16666666666666</v>
+        <v>21.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5521628498727735</v>
+        <v>0.3282442748091603</v>
       </c>
       <c r="Q5" t="n">
         <v>4.5</v>
@@ -1103,22 +1103,22 @@
         <v>1.833333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08396946564885496</v>
+        <v>0.08905852417302798</v>
       </c>
       <c r="Z5" t="n">
         <v>7.833333333333333</v>
       </c>
       <c r="AA5" t="n">
-        <v>25.33333333333333</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3867684478371501</v>
+        <v>0.3816793893129771</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8248847926267281</v>
+        <v>0.7054263565891472</v>
       </c>
       <c r="AD5" t="n">
         <v>0.3970588235294117</v>
@@ -1127,13 +1127,13 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3092105263157895</v>
+        <v>0.3133333333333333</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.649769585253456</v>
+        <v>1.410852713178294</v>
       </c>
       <c r="AI5" t="n">
         <v>1.272727272727273</v>
@@ -1498,13 +1498,13 @@
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.667</v>
+        <v>0.556</v>
       </c>
       <c r="AB8" t="n">
         <v>4</v>
@@ -1828,13 +1828,13 @@
         <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1855,22 +1855,22 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1993,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
         <v>1</v>
@@ -2158,13 +2158,13 @@
         <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.826</v>
+        <v>0.5</v>
       </c>
       <c r="AB12" t="n">
         <v>10</v>
@@ -2185,22 +2185,22 @@
         <v>0.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.297</v>
+        <v>0.278</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -2323,13 +2323,13 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AB13" t="n">
         <v>5</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2362,10 +2362,10 @@
         <v>5</v>
       </c>
       <c r="AL13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.417</v>
+        <v>0.455</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.533</v>
+        <v>0.3</v>
       </c>
       <c r="AB14" t="n">
         <v>3</v>
@@ -2653,13 +2653,13 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="AB15" t="n">
         <v>8</v>
@@ -2818,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.706</v>
+        <v>0.63</v>
       </c>
       <c r="AB16" t="n">
         <v>3</v>
@@ -2983,13 +2983,13 @@
         <v>1</v>
       </c>
       <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
         <v>4</v>
       </c>
-      <c r="Z17" t="n">
-        <v>6</v>
-      </c>
       <c r="AA17" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3148,13 +3148,13 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.727</v>
+        <v>0.7</v>
       </c>
       <c r="AB18" t="n">
         <v>1</v>
@@ -3973,13 +3973,13 @@
         <v>17</v>
       </c>
       <c r="Y23" t="n">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="Z23" t="n">
-        <v>209</v>
+        <v>142</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.718</v>
+        <v>0.585</v>
       </c>
       <c r="AB23" t="n">
         <v>41</v>
@@ -4000,22 +4000,22 @@
         <v>0.471</v>
       </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.227</v>
+        <v>0.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AL23" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.352</v>
+        <v>0.345</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4138,13 +4138,13 @@
         <v>56</v>
       </c>
       <c r="Y24" t="n">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="Z24" t="n">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.825</v>
+        <v>0.705</v>
       </c>
       <c r="AB24" t="n">
         <v>27</v>
@@ -4168,19 +4168,19 @@
         <v>11</v>
       </c>
       <c r="AI24" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.333</v>
+        <v>0.314</v>
       </c>
       <c r="AK24" t="n">
         <v>47</v>
       </c>
       <c r="AL24" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.309</v>
+        <v>0.313</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4362,13 +4362,13 @@
         <v>0.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.667</v>
+        <v>0.556</v>
       </c>
       <c r="AB26" t="n">
         <v>0.667</v>
@@ -4692,13 +4692,13 @@
         <v>0.333</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AB28" t="n">
         <v>0.833</v>
@@ -4719,22 +4719,22 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="AL28" t="n">
-        <v>3.5</v>
+        <v>3.333</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -4857,10 +4857,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
         <v>1</v>
@@ -5022,13 +5022,13 @@
         <v>0.667</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.167</v>
+        <v>0.667</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.833</v>
+        <v>1.333</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.826</v>
+        <v>0.5</v>
       </c>
       <c r="AB30" t="n">
         <v>1.667</v>
@@ -5049,22 +5049,22 @@
         <v>0.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.833</v>
+        <v>1.667</v>
       </c>
       <c r="AL30" t="n">
-        <v>6.167</v>
+        <v>6</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.297</v>
+        <v>0.278</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5187,13 +5187,13 @@
         <v>0.167</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.333</v>
+        <v>0.667</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AB31" t="n">
         <v>0.833</v>
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AJ31" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0.833</v>
       </c>
       <c r="AL31" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.417</v>
+        <v>0.455</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>0.167</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.333</v>
+        <v>0.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.5</v>
+        <v>1.667</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.533</v>
+        <v>0.3</v>
       </c>
       <c r="AB32" t="n">
         <v>0.5</v>
@@ -5517,13 +5517,13 @@
         <v>0.167</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.833</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.167</v>
+        <v>3.333</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="AB33" t="n">
         <v>1.333</v>
@@ -5682,13 +5682,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>4</v>
+        <v>2.833</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.667</v>
+        <v>4.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.706</v>
+        <v>0.63</v>
       </c>
       <c r="AB34" t="n">
         <v>0.5</v>
@@ -5847,13 +5847,13 @@
         <v>0.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -6012,13 +6012,13 @@
         <v>0.167</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.333</v>
+        <v>1.167</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.833</v>
+        <v>1.667</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.727</v>
+        <v>0.7</v>
       </c>
       <c r="AB36" t="n">
         <v>0.167</v>
@@ -6837,13 +6837,13 @@
         <v>2.833</v>
       </c>
       <c r="Y41" t="n">
-        <v>25</v>
+        <v>13.833</v>
       </c>
       <c r="Z41" t="n">
-        <v>34.833</v>
+        <v>23.667</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.718</v>
+        <v>0.585</v>
       </c>
       <c r="AB41" t="n">
         <v>6.833</v>
@@ -6864,22 +6864,22 @@
         <v>0.471</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.833</v>
+        <v>1.167</v>
       </c>
       <c r="AI41" t="n">
-        <v>3.667</v>
+        <v>4.167</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.227</v>
+        <v>0.28</v>
       </c>
       <c r="AK41" t="n">
-        <v>8.5</v>
+        <v>8.167</v>
       </c>
       <c r="AL41" t="n">
-        <v>24.167</v>
+        <v>23.667</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.352</v>
+        <v>0.345</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -7002,13 +7002,13 @@
         <v>9.333</v>
       </c>
       <c r="Y42" t="n">
-        <v>29.833</v>
+        <v>15.167</v>
       </c>
       <c r="Z42" t="n">
-        <v>36.167</v>
+        <v>21.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.825</v>
+        <v>0.705</v>
       </c>
       <c r="AB42" t="n">
         <v>4.5</v>
@@ -7032,19 +7032,19 @@
         <v>1.833</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.5</v>
+        <v>5.833</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.333</v>
+        <v>0.314</v>
       </c>
       <c r="AK42" t="n">
         <v>7.833</v>
       </c>
       <c r="AL42" t="n">
-        <v>25.333</v>
+        <v>25</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.309</v>
+        <v>0.313</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
